--- a/output/result_qingyuan.xlsx
+++ b/output/result_qingyuan.xlsx
@@ -581,12 +581,12 @@
     <row r="2" ht="26" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>未知</t>
+          <t>清远</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
